--- a/data/fokito/calendario.xlsx
+++ b/data/fokito/calendario.xlsx
@@ -3586,7 +3586,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>Trabajo Autónomo</t>
+          <t>no hay</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr"/>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>Trabajo Autónomo</t>
+          <t>Trabajo Exploratorio 1</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr"/>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>Trabajo Exploratorio 1</t>
+          <t>no hay</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr"/>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>Laboratorio 6</t>
+          <t>laboratorio 6</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr"/>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>Laboratorio 7</t>
+          <t>laboratorio 7</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr"/>

--- a/data/fokito/calendario.xlsx
+++ b/data/fokito/calendario.xlsx
@@ -517,7 +517,7 @@
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -608,7 +608,7 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -652,7 +652,7 @@
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
@@ -692,7 +692,7 @@
       <c r="H4" s="8" t="inlineStr"/>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
@@ -736,7 +736,7 @@
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -776,7 +776,7 @@
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr"/>
@@ -816,7 +816,7 @@
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr"/>
@@ -856,7 +856,7 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -896,7 +896,7 @@
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
@@ -936,7 +936,7 @@
       <c r="H10" s="8" t="inlineStr"/>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -980,7 +980,7 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
       <c r="H13" s="8" t="inlineStr"/>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
       <c r="H16" s="8" t="inlineStr"/>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1224,7 +1224,7 @@
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1264,7 +1264,7 @@
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr"/>
@@ -1304,7 +1304,7 @@
       <c r="H19" s="8" t="inlineStr"/>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr"/>
@@ -1344,7 +1344,7 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
       <c r="H22" s="8" t="inlineStr"/>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -1508,7 +1508,7 @@
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       <c r="H25" s="8" t="inlineStr"/>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1628,7 +1628,7 @@
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
@@ -1668,7 +1668,7 @@
       <c r="H28" s="8" t="inlineStr"/>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1712,7 +1712,7 @@
       <c r="H29" s="11" t="inlineStr"/>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
@@ -1756,7 +1756,7 @@
       <c r="H30" s="11" t="inlineStr"/>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
@@ -1800,7 +1800,7 @@
       <c r="H31" s="11" t="inlineStr"/>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -1844,7 +1844,7 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -1884,7 +1884,7 @@
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
@@ -1924,7 +1924,7 @@
       <c r="H34" s="8" t="inlineStr"/>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -1968,7 +1968,7 @@
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr"/>
@@ -2048,7 +2048,7 @@
       <c r="H37" s="8" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
@@ -2168,7 +2168,7 @@
       <c r="H40" s="8" t="inlineStr"/>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -2212,7 +2212,7 @@
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -2252,7 +2252,7 @@
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr"/>
@@ -2292,7 +2292,7 @@
       <c r="H43" s="8" t="inlineStr"/>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -2372,7 +2372,7 @@
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       <c r="H46" s="8" t="inlineStr"/>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
@@ -2456,7 +2456,7 @@
       <c r="H47" s="11" t="inlineStr"/>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
@@ -2500,7 +2500,7 @@
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr"/>
@@ -2540,7 +2540,7 @@
       <c r="H49" s="8" t="inlineStr"/>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr"/>
@@ -2580,7 +2580,7 @@
       <c r="H50" s="14" t="inlineStr"/>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
@@ -2624,7 +2624,7 @@
       <c r="H51" s="14" t="inlineStr"/>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J51" s="14" t="inlineStr">
@@ -2668,7 +2668,7 @@
       <c r="H52" s="14" t="inlineStr"/>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J52" s="14" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr"/>
@@ -2800,7 +2800,7 @@
       <c r="H55" s="8" t="inlineStr"/>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J55" s="8" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JM, MB, NV</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr"/>
@@ -2928,7 +2928,7 @@
       <c r="H58" s="8" t="inlineStr"/>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>IG, NV, GM, VB</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr"/>
@@ -2968,7 +2968,7 @@
       <c r="H59" s="8" t="inlineStr"/>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -3012,7 +3012,7 @@
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr"/>
@@ -3096,7 +3096,7 @@
       <c r="H62" s="8" t="inlineStr"/>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
@@ -3140,7 +3140,7 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
       <c r="H65" s="8" t="inlineStr"/>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
@@ -3264,7 +3264,7 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -3304,7 +3304,7 @@
       <c r="H67" s="11" t="inlineStr"/>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
@@ -3348,7 +3348,7 @@
       <c r="H68" s="8" t="inlineStr"/>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr"/>
@@ -3388,7 +3388,7 @@
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
@@ -3428,7 +3428,7 @@
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr"/>
@@ -3468,7 +3468,7 @@
       <c r="H71" s="8" t="inlineStr"/>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -3512,7 +3512,7 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -3552,7 +3552,7 @@
       <c r="H73" s="5" t="inlineStr"/>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
       <c r="H74" s="8" t="inlineStr"/>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
@@ -3636,7 +3636,7 @@
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
@@ -3724,7 +3724,7 @@
       <c r="H77" s="8" t="inlineStr"/>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr">
@@ -3768,7 +3768,7 @@
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -3808,7 +3808,7 @@
       <c r="H79" s="11" t="inlineStr"/>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
@@ -3852,7 +3852,7 @@
       <c r="H80" s="8" t="inlineStr"/>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J80" s="8" t="inlineStr">
@@ -3896,7 +3896,7 @@
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -3936,7 +3936,7 @@
       <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr"/>
@@ -3976,7 +3976,7 @@
       <c r="H83" s="8" t="inlineStr"/>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
@@ -4020,7 +4020,7 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
@@ -4060,7 +4060,7 @@
       <c r="H85" s="5" t="inlineStr"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr"/>
@@ -4100,7 +4100,7 @@
       <c r="H86" s="11" t="inlineStr"/>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr">
@@ -4144,7 +4144,7 @@
       <c r="H87" s="11" t="inlineStr"/>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
@@ -4188,7 +4188,7 @@
       <c r="H88" s="11" t="inlineStr"/>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J88" s="11" t="inlineStr">
@@ -4232,7 +4232,7 @@
       <c r="H89" s="8" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
@@ -4276,7 +4276,7 @@
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
@@ -4316,7 +4316,7 @@
       <c r="H91" s="5" t="inlineStr"/>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       <c r="H92" s="8" t="inlineStr"/>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr"/>
@@ -4396,7 +4396,7 @@
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
@@ -4436,7 +4436,7 @@
       <c r="H94" s="5" t="inlineStr"/>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr"/>
@@ -4476,7 +4476,7 @@
       <c r="H95" s="8" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J95" s="8" t="inlineStr"/>
@@ -4516,7 +4516,7 @@
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
@@ -4556,7 +4556,7 @@
       <c r="H97" s="5" t="inlineStr"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr"/>
@@ -4596,7 +4596,7 @@
       <c r="H98" s="8" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
@@ -4640,7 +4640,7 @@
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -4680,7 +4680,7 @@
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr"/>
@@ -4720,7 +4720,7 @@
       <c r="H101" s="8" t="inlineStr"/>
       <c r="I101" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J101" s="8" t="inlineStr">
@@ -4764,7 +4764,7 @@
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -4804,7 +4804,7 @@
       <c r="H103" s="5" t="inlineStr"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr"/>
@@ -4844,7 +4844,7 @@
       <c r="H104" s="11" t="inlineStr"/>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J104" s="11" t="inlineStr">
@@ -4888,7 +4888,7 @@
       <c r="H105" s="11" t="inlineStr"/>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J105" s="11" t="inlineStr">
@@ -4932,7 +4932,7 @@
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr"/>
@@ -4972,7 +4972,7 @@
       <c r="H107" s="14" t="inlineStr"/>
       <c r="I107" s="14" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J107" s="14" t="inlineStr">
@@ -5016,7 +5016,7 @@
       <c r="H108" s="14" t="inlineStr"/>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J108" s="14" t="inlineStr">
@@ -5060,7 +5060,7 @@
       <c r="H109" s="14" t="inlineStr"/>
       <c r="I109" s="14" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J109" s="14" t="inlineStr">
@@ -5104,7 +5104,7 @@
       <c r="H110" s="8" t="inlineStr"/>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr"/>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr"/>
@@ -5232,7 +5232,7 @@
       <c r="H113" s="8" t="inlineStr"/>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>JCS, GM, VB, XX</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr"/>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -5320,7 +5320,7 @@
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr"/>
@@ -5360,7 +5360,7 @@
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr"/>
@@ -5400,7 +5400,7 @@
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr"/>
@@ -5440,7 +5440,7 @@
       <c r="H118" s="8" t="inlineStr"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
@@ -5484,7 +5484,7 @@
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr"/>
@@ -5524,7 +5524,7 @@
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr"/>
@@ -5564,7 +5564,7 @@
       <c r="H121" s="8" t="inlineStr"/>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J121" s="8" t="inlineStr">
@@ -5608,7 +5608,7 @@
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr"/>
@@ -5648,7 +5648,7 @@
       <c r="H123" s="11" t="inlineStr"/>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J123" s="11" t="inlineStr">
@@ -5692,7 +5692,7 @@
       <c r="H124" s="11" t="inlineStr"/>
       <c r="I124" s="11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J124" s="11" t="inlineStr">
@@ -5736,7 +5736,7 @@
       <c r="H125" s="2" t="inlineStr"/>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr"/>
@@ -5776,7 +5776,7 @@
       <c r="H126" s="5" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr"/>
@@ -5816,7 +5816,7 @@
       <c r="H127" s="8" t="inlineStr"/>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J127" s="8" t="inlineStr"/>
@@ -5856,7 +5856,7 @@
       <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr"/>
@@ -5896,7 +5896,7 @@
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr"/>
@@ -5936,7 +5936,7 @@
       <c r="H130" s="8" t="inlineStr"/>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
@@ -5980,7 +5980,7 @@
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr"/>
@@ -6020,7 +6020,7 @@
       <c r="H132" s="5" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr"/>
@@ -6060,7 +6060,7 @@
       <c r="H133" s="8" t="inlineStr"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J133" s="8" t="inlineStr"/>
@@ -6100,7 +6100,7 @@
       <c r="H134" s="2" t="inlineStr"/>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
@@ -6140,7 +6140,7 @@
       <c r="H135" s="11" t="inlineStr"/>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J135" s="11" t="inlineStr">
@@ -6184,7 +6184,7 @@
       <c r="H136" s="11" t="inlineStr"/>
       <c r="I136" s="11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J136" s="11" t="inlineStr">
@@ -6228,7 +6228,7 @@
       <c r="H137" s="2" t="inlineStr"/>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr"/>
@@ -6268,7 +6268,7 @@
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr"/>
@@ -6308,7 +6308,7 @@
       <c r="H139" s="8" t="inlineStr"/>
       <c r="I139" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J139" s="8" t="inlineStr">
@@ -6352,7 +6352,7 @@
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr"/>
@@ -6392,7 +6392,7 @@
       <c r="H141" s="5" t="inlineStr"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J141" s="5" t="inlineStr"/>
@@ -6432,7 +6432,7 @@
       <c r="H142" s="8" t="inlineStr"/>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J142" s="8" t="inlineStr">
@@ -6476,7 +6476,7 @@
       <c r="H143" s="11" t="inlineStr"/>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J143" s="11" t="inlineStr">
@@ -6520,7 +6520,7 @@
       <c r="H144" s="11" t="inlineStr"/>
       <c r="I144" s="11" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J144" s="11" t="inlineStr">
@@ -6564,7 +6564,7 @@
       <c r="H145" s="11" t="inlineStr"/>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J145" s="11" t="inlineStr">
@@ -6608,7 +6608,7 @@
       <c r="H146" s="2" t="inlineStr"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr"/>
@@ -6648,7 +6648,7 @@
       <c r="H147" s="5" t="inlineStr"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr"/>
@@ -6688,7 +6688,7 @@
       <c r="H148" s="8" t="inlineStr"/>
       <c r="I148" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J148" s="8" t="inlineStr">
@@ -6732,7 +6732,7 @@
       <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr"/>
@@ -6772,7 +6772,7 @@
       <c r="H150" s="5" t="inlineStr"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J150" s="5" t="inlineStr"/>
@@ -6812,7 +6812,7 @@
       <c r="H151" s="8" t="inlineStr"/>
       <c r="I151" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J151" s="8" t="inlineStr"/>
@@ -6852,7 +6852,7 @@
       <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr"/>
@@ -6892,7 +6892,7 @@
       <c r="H153" s="5" t="inlineStr"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr"/>
@@ -6932,7 +6932,7 @@
       <c r="H154" s="8" t="inlineStr"/>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J154" s="8" t="inlineStr">
@@ -6976,7 +6976,7 @@
       <c r="H155" s="2" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr"/>
@@ -7016,7 +7016,7 @@
       <c r="H156" s="5" t="inlineStr"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J156" s="5" t="inlineStr"/>
@@ -7056,7 +7056,7 @@
       <c r="H157" s="8" t="inlineStr"/>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J157" s="8" t="inlineStr"/>
@@ -7096,7 +7096,7 @@
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr"/>
@@ -7136,7 +7136,7 @@
       <c r="H159" s="5" t="inlineStr"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr"/>
@@ -7176,7 +7176,7 @@
       <c r="H160" s="8" t="inlineStr"/>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J160" s="8" t="inlineStr">
@@ -7220,7 +7220,7 @@
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr"/>
@@ -7260,7 +7260,7 @@
       <c r="H162" s="5" t="inlineStr"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J162" s="5" t="inlineStr"/>
@@ -7300,7 +7300,7 @@
       <c r="H163" s="8" t="inlineStr"/>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J163" s="8" t="inlineStr"/>
@@ -7340,7 +7340,7 @@
       <c r="H164" s="14" t="inlineStr"/>
       <c r="I164" s="14" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J164" s="14" t="inlineStr">
@@ -7384,7 +7384,7 @@
       <c r="H165" s="14" t="inlineStr"/>
       <c r="I165" s="14" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J165" s="14" t="inlineStr">
@@ -7428,7 +7428,7 @@
       <c r="H166" s="14" t="inlineStr"/>
       <c r="I166" s="14" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J166" s="14" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       <c r="H168" s="5" t="inlineStr"/>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr"/>
@@ -7560,7 +7560,7 @@
       <c r="H169" s="8" t="inlineStr"/>
       <c r="I169" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J169" s="8" t="inlineStr"/>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       <c r="H171" s="5" t="inlineStr"/>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>EG, RM, XX</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr"/>
@@ -7688,7 +7688,7 @@
       <c r="H172" s="8" t="inlineStr"/>
       <c r="I172" s="8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>EG, AR, XX, XX</t>
         </is>
       </c>
       <c r="J172" s="8" t="inlineStr"/>
@@ -7728,7 +7728,7 @@
       <c r="H173" s="2" t="inlineStr"/>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       <c r="H174" s="8" t="inlineStr"/>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J174" s="8" t="inlineStr">
@@ -7816,7 +7816,7 @@
       <c r="H175" s="5" t="inlineStr"/>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J175" s="5" t="inlineStr">
@@ -7860,7 +7860,7 @@
       <c r="H176" s="2" t="inlineStr"/>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr"/>
@@ -7900,7 +7900,7 @@
       <c r="H177" s="8" t="inlineStr"/>
       <c r="I177" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J177" s="8" t="inlineStr">
@@ -7944,7 +7944,7 @@
       <c r="H178" s="5" t="inlineStr"/>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr"/>
@@ -7984,7 +7984,7 @@
       <c r="H179" s="2" t="inlineStr"/>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr"/>
@@ -8024,7 +8024,7 @@
       <c r="H180" s="11" t="inlineStr"/>
       <c r="I180" s="11" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J180" s="11" t="inlineStr">
@@ -8068,7 +8068,7 @@
       <c r="H181" s="11" t="inlineStr"/>
       <c r="I181" s="11" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J181" s="11" t="inlineStr">
@@ -8112,7 +8112,7 @@
       <c r="H182" s="2" t="inlineStr"/>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr"/>
@@ -8152,7 +8152,7 @@
       <c r="H183" s="8" t="inlineStr"/>
       <c r="I183" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J183" s="8" t="inlineStr">
@@ -8196,7 +8196,7 @@
       <c r="H184" s="5" t="inlineStr"/>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J184" s="5" t="inlineStr"/>
@@ -8236,7 +8236,7 @@
       <c r="H185" s="2" t="inlineStr"/>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr"/>
@@ -8276,7 +8276,7 @@
       <c r="H186" s="8" t="inlineStr"/>
       <c r="I186" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J186" s="8" t="inlineStr"/>
@@ -8316,7 +8316,7 @@
       <c r="H187" s="5" t="inlineStr"/>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J187" s="5" t="inlineStr"/>
@@ -8356,7 +8356,7 @@
       <c r="H188" s="2" t="inlineStr"/>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr"/>
@@ -8396,7 +8396,7 @@
       <c r="H189" s="8" t="inlineStr"/>
       <c r="I189" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J189" s="8" t="inlineStr">
@@ -8440,7 +8440,7 @@
       <c r="H190" s="5" t="inlineStr"/>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J190" s="5" t="inlineStr"/>
@@ -8480,7 +8480,7 @@
       <c r="H191" s="2" t="inlineStr"/>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr"/>
@@ -8520,7 +8520,7 @@
       <c r="H192" s="11" t="inlineStr"/>
       <c r="I192" s="11" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J192" s="11" t="inlineStr">
@@ -8564,7 +8564,7 @@
       <c r="H193" s="11" t="inlineStr"/>
       <c r="I193" s="11" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J193" s="11" t="inlineStr">
@@ -8608,7 +8608,7 @@
       <c r="H194" s="2" t="inlineStr"/>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr"/>
@@ -8648,7 +8648,7 @@
       <c r="H195" s="8" t="inlineStr"/>
       <c r="I195" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J195" s="8" t="inlineStr">
@@ -8692,7 +8692,7 @@
       <c r="H196" s="5" t="inlineStr"/>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J196" s="5" t="inlineStr"/>
@@ -8732,7 +8732,7 @@
       <c r="H197" s="2" t="inlineStr"/>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr"/>
@@ -8772,7 +8772,7 @@
       <c r="H198" s="8" t="inlineStr"/>
       <c r="I198" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J198" s="8" t="inlineStr">
@@ -8816,7 +8816,7 @@
       <c r="H199" s="5" t="inlineStr"/>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J199" s="5" t="inlineStr"/>
@@ -8856,7 +8856,7 @@
       <c r="H200" s="11" t="inlineStr"/>
       <c r="I200" s="11" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J200" s="11" t="inlineStr">
@@ -8900,7 +8900,7 @@
       <c r="H201" s="11" t="inlineStr"/>
       <c r="I201" s="11" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J201" s="11" t="inlineStr">
@@ -8944,7 +8944,7 @@
       <c r="H202" s="11" t="inlineStr"/>
       <c r="I202" s="11" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J202" s="11" t="inlineStr">
@@ -8988,7 +8988,7 @@
       <c r="H203" s="2" t="inlineStr"/>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr"/>
@@ -9028,7 +9028,7 @@
       <c r="H204" s="8" t="inlineStr"/>
       <c r="I204" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J204" s="8" t="inlineStr">
@@ -9072,7 +9072,7 @@
       <c r="H205" s="5" t="inlineStr"/>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J205" s="5" t="inlineStr"/>
@@ -9112,7 +9112,7 @@
       <c r="H206" s="2" t="inlineStr"/>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr"/>
@@ -9152,7 +9152,7 @@
       <c r="H207" s="8" t="inlineStr"/>
       <c r="I207" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J207" s="8" t="inlineStr"/>
@@ -9192,7 +9192,7 @@
       <c r="H208" s="5" t="inlineStr"/>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J208" s="5" t="inlineStr"/>
@@ -9232,7 +9232,7 @@
       <c r="H209" s="2" t="inlineStr"/>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J209" s="2" t="inlineStr"/>
@@ -9272,7 +9272,7 @@
       <c r="H210" s="8" t="inlineStr"/>
       <c r="I210" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J210" s="8" t="inlineStr">
@@ -9316,7 +9316,7 @@
       <c r="H211" s="5" t="inlineStr"/>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J211" s="5" t="inlineStr"/>
@@ -9356,7 +9356,7 @@
       <c r="H212" s="2" t="inlineStr"/>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr"/>
@@ -9396,7 +9396,7 @@
       <c r="H213" s="8" t="inlineStr"/>
       <c r="I213" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J213" s="8" t="inlineStr"/>
@@ -9436,7 +9436,7 @@
       <c r="H214" s="5" t="inlineStr"/>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J214" s="5" t="inlineStr"/>
@@ -9476,7 +9476,7 @@
       <c r="H215" s="2" t="inlineStr"/>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr"/>
@@ -9516,7 +9516,7 @@
       <c r="H216" s="8" t="inlineStr"/>
       <c r="I216" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J216" s="8" t="inlineStr"/>
@@ -9556,7 +9556,7 @@
       <c r="H217" s="5" t="inlineStr"/>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J217" s="5" t="inlineStr"/>
@@ -9596,7 +9596,7 @@
       <c r="H218" s="2" t="inlineStr"/>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr"/>
@@ -9636,7 +9636,7 @@
       <c r="H219" s="8" t="inlineStr"/>
       <c r="I219" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J219" s="8" t="inlineStr"/>
@@ -9676,7 +9676,7 @@
       <c r="H220" s="5" t="inlineStr"/>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J220" s="5" t="inlineStr"/>
@@ -9716,7 +9716,7 @@
       <c r="H221" s="14" t="inlineStr"/>
       <c r="I221" s="14" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J221" s="14" t="inlineStr">
@@ -9760,7 +9760,7 @@
       <c r="H222" s="14" t="inlineStr"/>
       <c r="I222" s="14" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J222" s="14" t="inlineStr">
@@ -9804,7 +9804,7 @@
       <c r="H223" s="14" t="inlineStr"/>
       <c r="I223" s="14" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J223" s="14" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
@@ -9896,7 +9896,7 @@
       <c r="H225" s="8" t="inlineStr"/>
       <c r="I225" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J225" s="8" t="inlineStr"/>
@@ -9936,7 +9936,7 @@
       <c r="H226" s="5" t="inlineStr"/>
       <c r="I226" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J226" s="5" t="inlineStr"/>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       <c r="H228" s="8" t="inlineStr"/>
       <c r="I228" s="8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG, SM, CC, XX</t>
         </is>
       </c>
       <c r="J228" s="8" t="inlineStr"/>
@@ -10064,7 +10064,7 @@
       <c r="H229" s="5" t="inlineStr"/>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SM, XX, XX</t>
         </is>
       </c>
       <c r="J229" s="5" t="inlineStr"/>

--- a/data/fokito/calendario.xlsx
+++ b/data/fokito/calendario.xlsx
@@ -648,7 +648,7 @@
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1764,7 +1764,7 @@
       <c r="H30" s="12" t="inlineStr"/>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
@@ -1892,7 +1892,7 @@
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -2140,7 +2140,7 @@
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -2388,7 +2388,7 @@
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       <c r="H52" s="15" t="inlineStr"/>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J52" s="15" t="inlineStr">
@@ -2820,7 +2820,7 @@
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr"/>
@@ -2948,7 +2948,7 @@
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>JM, MB, NV</t>
+          <t>JM, NV, MB</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr"/>
@@ -5472,7 +5472,7 @@
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr"/>
@@ -5512,7 +5512,7 @@
       <c r="H119" s="8" t="inlineStr"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr"/>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
@@ -5640,7 +5640,7 @@
       <c r="H122" s="8" t="inlineStr"/>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr"/>
@@ -5720,7 +5720,7 @@
       <c r="H124" s="12" t="inlineStr"/>
       <c r="I124" s="12" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J124" s="12" t="inlineStr">
@@ -5764,7 +5764,7 @@
       <c r="H125" s="12" t="inlineStr"/>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr"/>
@@ -5888,7 +5888,7 @@
       <c r="H128" s="8" t="inlineStr"/>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr"/>
@@ -5968,7 +5968,7 @@
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr"/>
@@ -6008,7 +6008,7 @@
       <c r="H131" s="8" t="inlineStr"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J131" s="8" t="inlineStr"/>
@@ -6088,7 +6088,7 @@
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr"/>
@@ -6128,7 +6128,7 @@
       <c r="H134" s="8" t="inlineStr"/>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr"/>
@@ -6248,7 +6248,7 @@
       <c r="H137" s="12" t="inlineStr"/>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J137" s="12" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="I138" s="12" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J138" s="12" t="inlineStr">
@@ -6380,7 +6380,7 @@
       <c r="H140" s="5" t="inlineStr"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr"/>
@@ -6420,7 +6420,7 @@
       <c r="H141" s="8" t="inlineStr"/>
       <c r="I141" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J141" s="8" t="inlineStr"/>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
@@ -6548,7 +6548,7 @@
       <c r="H144" s="8" t="inlineStr"/>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J144" s="8" t="inlineStr"/>
@@ -6632,7 +6632,7 @@
       <c r="H146" s="12" t="inlineStr"/>
       <c r="I146" s="12" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J146" s="12" t="inlineStr">
@@ -6676,7 +6676,7 @@
       <c r="H147" s="12" t="inlineStr"/>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
@@ -6760,7 +6760,7 @@
       <c r="H149" s="5" t="inlineStr"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr"/>
@@ -6800,7 +6800,7 @@
       <c r="H150" s="8" t="inlineStr"/>
       <c r="I150" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J150" s="8" t="inlineStr"/>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
@@ -6928,7 +6928,7 @@
       <c r="H153" s="8" t="inlineStr"/>
       <c r="I153" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J153" s="8" t="inlineStr"/>
@@ -7008,7 +7008,7 @@
       <c r="H155" s="5" t="inlineStr"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr"/>
@@ -7048,7 +7048,7 @@
       <c r="H156" s="8" t="inlineStr"/>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J156" s="8" t="inlineStr"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
@@ -7176,7 +7176,7 @@
       <c r="H159" s="8" t="inlineStr"/>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J159" s="8" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
       <c r="H161" s="5" t="inlineStr"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J161" s="5" t="inlineStr"/>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J165" s="8" t="inlineStr">
@@ -7524,7 +7524,7 @@
       <c r="H167" s="15" t="inlineStr"/>
       <c r="I167" s="15" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J167" s="15" t="inlineStr">
@@ -7568,7 +7568,7 @@
       <c r="H168" s="15" t="inlineStr"/>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J168" s="15" t="inlineStr">
@@ -7660,7 +7660,7 @@
       <c r="H170" s="5" t="inlineStr"/>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr"/>
@@ -7700,7 +7700,7 @@
       <c r="H171" s="8" t="inlineStr"/>
       <c r="I171" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J171" s="8" t="inlineStr"/>
@@ -7788,7 +7788,7 @@
       <c r="H173" s="5" t="inlineStr"/>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>EG, RM, XX</t>
+          <t>JM, NV, EG</t>
         </is>
       </c>
       <c r="J173" s="5" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       <c r="H174" s="8" t="inlineStr"/>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>EG, AR, XX, XX</t>
+          <t>AR, JM, MB, EG</t>
         </is>
       </c>
       <c r="J174" s="8" t="inlineStr"/>
@@ -7948,7 +7948,7 @@
       <c r="H177" s="5" t="inlineStr"/>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
@@ -8200,7 +8200,7 @@
       <c r="H183" s="12" t="inlineStr"/>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J183" s="12" t="inlineStr">
@@ -8324,7 +8324,7 @@
       <c r="H186" s="5" t="inlineStr"/>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J186" s="5" t="inlineStr"/>
@@ -8444,7 +8444,7 @@
       <c r="H189" s="5" t="inlineStr"/>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J189" s="5" t="inlineStr"/>
@@ -8564,7 +8564,7 @@
       <c r="H192" s="5" t="inlineStr"/>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J192" s="5" t="inlineStr"/>
@@ -8732,7 +8732,7 @@
       <c r="H196" s="12" t="inlineStr"/>
       <c r="I196" s="12" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J196" s="12" t="inlineStr">
@@ -8856,7 +8856,7 @@
       <c r="H199" s="5" t="inlineStr"/>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J199" s="5" t="inlineStr"/>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="I202" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J202" s="5" t="inlineStr">
@@ -9112,7 +9112,7 @@
       <c r="H205" s="12" t="inlineStr"/>
       <c r="I205" s="12" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J205" s="12" t="inlineStr">
@@ -9236,7 +9236,7 @@
       <c r="H208" s="5" t="inlineStr"/>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J208" s="5" t="inlineStr"/>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J211" s="5" t="inlineStr">
@@ -9484,7 +9484,7 @@
       <c r="H214" s="5" t="inlineStr"/>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J214" s="5" t="inlineStr"/>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J217" s="5" t="inlineStr">
@@ -9740,7 +9740,7 @@
       <c r="H220" s="5" t="inlineStr"/>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J220" s="5" t="inlineStr"/>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J223" s="5" t="inlineStr">
@@ -10004,7 +10004,7 @@
       <c r="H226" s="15" t="inlineStr"/>
       <c r="I226" s="15" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J226" s="15" t="inlineStr">
@@ -10136,7 +10136,7 @@
       <c r="H229" s="5" t="inlineStr"/>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J229" s="5" t="inlineStr"/>
@@ -10264,7 +10264,7 @@
       <c r="H232" s="5" t="inlineStr"/>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>SM, XX, XX</t>
+          <t>RM, SM, XX</t>
         </is>
       </c>
       <c r="J232" s="5" t="inlineStr"/>

--- a/data/fokito/calendario.xlsx
+++ b/data/fokito/calendario.xlsx
@@ -3028,7 +3028,7 @@
       <c r="H60" s="8" t="inlineStr"/>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr"/>
@@ -3148,7 +3148,7 @@
       <c r="H63" s="8" t="inlineStr"/>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       <c r="H66" s="8" t="inlineStr"/>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr"/>
@@ -3400,7 +3400,7 @@
       <c r="H69" s="8" t="inlineStr"/>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       <c r="H72" s="8" t="inlineStr"/>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr"/>
@@ -3640,7 +3640,7 @@
       <c r="H75" s="8" t="inlineStr"/>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J75" s="8" t="inlineStr"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
@@ -3900,7 +3900,7 @@
       <c r="H81" s="8" t="inlineStr"/>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="H84" s="8" t="inlineStr"/>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr"/>
@@ -4152,7 +4152,7 @@
       <c r="H87" s="12" t="inlineStr"/>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J87" s="12" t="inlineStr">
@@ -4284,7 +4284,7 @@
       <c r="H90" s="8" t="inlineStr"/>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr"/>
@@ -4404,7 +4404,7 @@
       <c r="H93" s="8" t="inlineStr"/>
       <c r="I93" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J93" s="8" t="inlineStr"/>
@@ -4532,7 +4532,7 @@
       <c r="H96" s="8" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr"/>
@@ -4652,7 +4652,7 @@
       <c r="H99" s="8" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr"/>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
@@ -4908,7 +4908,7 @@
       <c r="H105" s="12" t="inlineStr"/>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J105" s="12" t="inlineStr">
@@ -5044,7 +5044,7 @@
       <c r="H108" s="15" t="inlineStr"/>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J108" s="15" t="inlineStr">
@@ -5176,7 +5176,7 @@
       <c r="H111" s="8" t="inlineStr"/>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr"/>
@@ -5304,7 +5304,7 @@
       <c r="H114" s="8" t="inlineStr"/>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>JCS, GM, VB, XX</t>
+          <t>JCS, GM, VB, EG</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr"/>
@@ -5472,7 +5472,7 @@
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr"/>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
@@ -5720,7 +5720,7 @@
       <c r="H124" s="12" t="inlineStr"/>
       <c r="I124" s="12" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J124" s="12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr"/>
@@ -5968,7 +5968,7 @@
       <c r="H130" s="5" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr"/>
@@ -6088,7 +6088,7 @@
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr"/>
@@ -6248,7 +6248,7 @@
       <c r="H137" s="12" t="inlineStr"/>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J137" s="12" t="inlineStr">
@@ -6380,7 +6380,7 @@
       <c r="H140" s="5" t="inlineStr"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr"/>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J143" s="5" t="inlineStr">
@@ -6632,7 +6632,7 @@
       <c r="H146" s="12" t="inlineStr"/>
       <c r="I146" s="12" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J146" s="12" t="inlineStr">
@@ -6760,7 +6760,7 @@
       <c r="H149" s="5" t="inlineStr"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J149" s="5" t="inlineStr"/>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J152" s="5" t="inlineStr">
@@ -7008,7 +7008,7 @@
       <c r="H155" s="5" t="inlineStr"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J155" s="5" t="inlineStr"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
@@ -7256,7 +7256,7 @@
       <c r="H161" s="5" t="inlineStr"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J161" s="5" t="inlineStr"/>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
@@ -7524,7 +7524,7 @@
       <c r="H167" s="15" t="inlineStr"/>
       <c r="I167" s="15" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J167" s="15" t="inlineStr">
@@ -7660,7 +7660,7 @@
       <c r="H170" s="5" t="inlineStr"/>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr"/>
@@ -7788,7 +7788,7 @@
       <c r="H173" s="5" t="inlineStr"/>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>JM, NV, EG</t>
+          <t>JM, NV, RM</t>
         </is>
       </c>
       <c r="J173" s="5" t="inlineStr"/>
@@ -7908,7 +7908,7 @@
       <c r="H176" s="8" t="inlineStr"/>
       <c r="I176" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J176" s="8" t="inlineStr"/>
@@ -7948,7 +7948,7 @@
       <c r="H177" s="5" t="inlineStr"/>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr"/>
@@ -8028,7 +8028,7 @@
       <c r="H179" s="8" t="inlineStr"/>
       <c r="I179" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J179" s="8" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
@@ -8156,7 +8156,7 @@
       <c r="H182" s="12" t="inlineStr"/>
       <c r="I182" s="12" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J182" s="12" t="inlineStr">
@@ -8200,7 +8200,7 @@
       <c r="H183" s="12" t="inlineStr"/>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J183" s="12" t="inlineStr">
@@ -8284,7 +8284,7 @@
       <c r="H185" s="8" t="inlineStr"/>
       <c r="I185" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J185" s="8" t="inlineStr"/>
@@ -8324,7 +8324,7 @@
       <c r="H186" s="5" t="inlineStr"/>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J186" s="5" t="inlineStr"/>
@@ -8404,7 +8404,7 @@
       <c r="H188" s="8" t="inlineStr"/>
       <c r="I188" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J188" s="8" t="inlineStr"/>
@@ -8444,7 +8444,7 @@
       <c r="H189" s="5" t="inlineStr"/>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J189" s="5" t="inlineStr"/>
@@ -8524,7 +8524,7 @@
       <c r="H191" s="8" t="inlineStr"/>
       <c r="I191" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J191" s="8" t="inlineStr"/>
@@ -8564,7 +8564,7 @@
       <c r="H192" s="5" t="inlineStr"/>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J192" s="5" t="inlineStr"/>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="I195" s="12" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J195" s="12" t="inlineStr">
@@ -8732,7 +8732,7 @@
       <c r="H196" s="12" t="inlineStr"/>
       <c r="I196" s="12" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J196" s="12" t="inlineStr">
@@ -8816,7 +8816,7 @@
       <c r="H198" s="8" t="inlineStr"/>
       <c r="I198" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J198" s="8" t="inlineStr"/>
@@ -8856,7 +8856,7 @@
       <c r="H199" s="5" t="inlineStr"/>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J199" s="5" t="inlineStr"/>
@@ -8936,7 +8936,7 @@
       <c r="H201" s="8" t="inlineStr"/>
       <c r="I201" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J201" s="8" t="inlineStr"/>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="I202" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J202" s="5" t="inlineStr">
@@ -9068,7 +9068,7 @@
       <c r="H204" s="12" t="inlineStr"/>
       <c r="I204" s="12" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J204" s="12" t="inlineStr">
@@ -9112,7 +9112,7 @@
       <c r="H205" s="12" t="inlineStr"/>
       <c r="I205" s="12" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J205" s="12" t="inlineStr">
@@ -9196,7 +9196,7 @@
       <c r="H207" s="8" t="inlineStr"/>
       <c r="I207" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J207" s="8" t="inlineStr"/>
@@ -9236,7 +9236,7 @@
       <c r="H208" s="5" t="inlineStr"/>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J208" s="5" t="inlineStr"/>
@@ -9316,7 +9316,7 @@
       <c r="H210" s="8" t="inlineStr"/>
       <c r="I210" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J210" s="8" t="inlineStr"/>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J211" s="5" t="inlineStr">
@@ -9444,7 +9444,7 @@
       <c r="H213" s="8" t="inlineStr"/>
       <c r="I213" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J213" s="8" t="inlineStr"/>
@@ -9484,7 +9484,7 @@
       <c r="H214" s="5" t="inlineStr"/>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J214" s="5" t="inlineStr"/>
@@ -9564,7 +9564,7 @@
       <c r="H216" s="8" t="inlineStr"/>
       <c r="I216" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J216" s="8" t="inlineStr"/>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J217" s="5" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="I219" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J219" s="8" t="inlineStr">
@@ -9740,7 +9740,7 @@
       <c r="H220" s="5" t="inlineStr"/>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J220" s="5" t="inlineStr"/>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="I222" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J222" s="8" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J223" s="5" t="inlineStr">
@@ -9960,7 +9960,7 @@
       <c r="H225" s="15" t="inlineStr"/>
       <c r="I225" s="15" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J225" s="15" t="inlineStr">
@@ -10004,7 +10004,7 @@
       <c r="H226" s="15" t="inlineStr"/>
       <c r="I226" s="15" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J226" s="15" t="inlineStr">
@@ -10096,7 +10096,7 @@
       <c r="H228" s="8" t="inlineStr"/>
       <c r="I228" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J228" s="8" t="inlineStr"/>
@@ -10136,7 +10136,7 @@
       <c r="H229" s="5" t="inlineStr"/>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J229" s="5" t="inlineStr"/>
@@ -10224,7 +10224,7 @@
       <c r="H231" s="8" t="inlineStr"/>
       <c r="I231" s="8" t="inlineStr">
         <is>
-          <t>EG, SM, CC, XX</t>
+          <t>EG, SM, CC, GF</t>
         </is>
       </c>
       <c r="J231" s="8" t="inlineStr"/>
@@ -10264,7 +10264,7 @@
       <c r="H232" s="5" t="inlineStr"/>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>RM, SM, XX</t>
+          <t>EG, SM, GF</t>
         </is>
       </c>
       <c r="J232" s="5" t="inlineStr"/>

--- a/data/fokito/calendario.xlsx
+++ b/data/fokito/calendario.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Calendario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calendario'!$A$1:$J$253</definedName>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Trabajo Exploratorio 1</t>
+          <t>Sin Laboratorio</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Revisión Certamen 1</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Sin Laboratorio</t>
+          <t>Trabajo Exploratorio 1</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr"/>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>Trabajo Exploratorio 1</t>
+          <t>no hay</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>no hay</t>
+          <t>Trabajo Exploratorio 1</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr"/>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Revisión Certamen 1</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>Revisión Certamen 1</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr"/>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>Revisión Certamen 1</t>
+          <t>Modelos y Derivadas 4</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr"/>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>Modelos y Derivadas 4</t>
+          <t>Revisión Certamen 1</t>
         </is>
       </c>
       <c r="H221" s="11" t="inlineStr">
